--- a/tablas_con_fuentes_crudo/competidores_tecnologicos_crudo.xlsx
+++ b/tablas_con_fuentes_crudo/competidores_tecnologicos_crudo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f569b11a287a01cd/Documentos/Files freelance/NoCountry_2026/Tablas/para subir al repositorio/tablas_fuentes_crudo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33992D2D-B7E6-414E-930A-89F6A338377E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{33992D2D-B7E6-414E-930A-89F6A338377E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ABAEB50-38DA-4A36-B6DD-3819F5996478}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,12 +187,6 @@
     <t>costo_importación_e_impuestos</t>
   </si>
   <si>
-    <t>costo_site_prep_refracción_min</t>
-  </si>
-  <si>
-    <t>costo_site_prep_refracción_max</t>
-  </si>
-  <si>
     <t>num_procedimientos_anuales</t>
   </si>
   <si>
@@ -341,13 +335,19 @@
   </si>
   <si>
     <t>Cvar = kit cirugia + gastos intenacion + costo uso equipamiento</t>
+  </si>
+  <si>
+    <t>costo_site_prep_refacción_min</t>
+  </si>
+  <si>
+    <t>costo_site_prep_refacción_max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -395,18 +395,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -487,7 +475,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -522,25 +510,25 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1106,7 +1094,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
@@ -1115,28 +1103,28 @@
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1144,22 +1132,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H2" s="7">
         <v>2500000</v>
@@ -1187,7 +1175,7 @@
         <v>150000</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q2" s="7">
         <v>9250</v>
@@ -1198,22 +1186,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="F3" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H3" s="7">
         <v>1000000</v>
@@ -1241,7 +1229,7 @@
         <v>75000</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="7">
         <v>10000</v>
@@ -1252,22 +1240,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="F4" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H4" s="7">
         <v>1200000</v>
@@ -1295,7 +1283,7 @@
         <v>115000</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="7">
         <v>8250</v>
@@ -1306,22 +1294,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H5" s="7">
         <v>1500000</v>
@@ -1348,7 +1336,7 @@
         <v>100000</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="7">
         <v>11600</v>
@@ -1359,22 +1347,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H6" s="7">
         <v>1400000</v>
@@ -1401,7 +1389,7 @@
         <v>100000</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="7">
         <v>10300</v>
@@ -1412,22 +1400,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H7" s="7">
         <v>1500000</v>
@@ -1455,7 +1443,7 @@
         <v>170000</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="7">
         <v>8750</v>
@@ -1466,7 +1454,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
@@ -1474,7 +1462,7 @@
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="6"/>
@@ -1492,10 +1480,10 @@
     <row r="9" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G9" s="1"/>
       <c r="L9" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q9" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1503,39 +1491,39 @@
     </row>
     <row r="11" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="16"/>
       <c r="F11" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="16"/>
       <c r="F12" s="15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" s="16"/>
       <c r="G13" s="1"/>
@@ -1544,7 +1532,7 @@
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" s="16"/>
       <c r="G14" s="1"/>
